--- a/assets/资金对账导出不平.xlsx
+++ b/assets/资金对账导出不平.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
   <si>
     <t>对账数据来源</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t>交易类型</t>
+  </si>
+  <si>
+    <t>FundType</t>
   </si>
   <si>
     <t>对账结果</t>
@@ -689,19 +692,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="14" width="15" customWidth="1"/>
-    <col min="15" max="17" width="20" customWidth="1"/>
-    <col min="18" max="20" width="30" customWidth="1"/>
+    <col min="1" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="15" width="15" customWidth="1"/>
+    <col min="16" max="18" width="20" customWidth="1"/>
+    <col min="19" max="21" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" ht="41" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,11 +764,14 @@
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -787,102 +793,102 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -904,102 +910,102 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1017,57 +1023,57 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1089,50 +1095,50 @@
   <sheetData>
     <row r="1" ht="82" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>